--- a/human_resources_forms/015_employee_grievance_handling_evaluation_form--human_resources_forms.xlsx
+++ b/human_resources_forms/015_employee_grievance_handling_evaluation_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -888,8 +888,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -917,12 +917,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'category',_'comment':_'category'}</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Category', 'comment': 'Category'}</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'subcategory',_'comment':_'subcategory'}</t>
+          <t>subcategory</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Subcategory', 'comment': 'Subcategory'}</t>
+          <t>Subcategory</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'not_satisfied',_'comment':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Not Satisfied', 'comment': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'somewhat_satisfied',_'comment':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Somewhat Satisfied', 'comment': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'satisfied',_'comment':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Satisfied', 'comment': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'very_satisfied',_'comment':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Very Satisfied', 'comment': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'a',_'comment':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'A', 'comment': 'A'}</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'b',_'comment':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'B', 'comment': 'B'}</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'c',_'comment':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'C', 'comment': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'d',_'comment':_'d'}</t>
+          <t>d</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'D', 'comment': 'D'}</t>
+          <t>D</t>
         </is>
       </c>
     </row>
